--- a/光伏配储项目/电价数据/2026/巨力站.xlsx
+++ b/光伏配储项目/电价数据/2026/巨力站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.49385</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.71556</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.60305</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.61722</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.65452</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6592100000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.5998600000000001</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.59985</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.59992</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.37394</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>1.32299</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.3442</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>1.11507</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12644</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13377</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.06378</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10502</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15948</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.04983</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.57877</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.88176</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14664</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22831</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23364</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21751</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.52035</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.13725</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.54044</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6379199999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5193099999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73177</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.09044</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.00049</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.5875900000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65874</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.84211</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6213500000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.17771</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.3313</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.02434</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.21289</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.2591</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.46185</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6613300000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.71447</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.39972</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.1232</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8717200000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7968200000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75746</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5179900000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4695299999999999</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42555</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70957</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77292</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.48539</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91742</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49492</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51562</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50334</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50358</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46785</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7355700000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83239</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45883</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.42603</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.32202</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49827</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7693</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.98373</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.51527</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8853099999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8414199999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.71096</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.09719</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.06049</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02381</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46722</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8332200000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62512</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.63774</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.05428</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17978</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.7781699999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.09968</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.00159</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.1567</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.93471</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.98654</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.71687</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90326</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.90355</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.85736</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8650399999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.70014</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7848999999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80572</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.5084</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.48727</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.48817</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.37914</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.20931</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5959099999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.56899</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.59948</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.59146</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5925900000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.59437</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.5936399999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.5965199999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.59954</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.5958600000000001</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.59212</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.59723</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.5958600000000001</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.59884</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.59424</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.59456</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.59899</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.59651</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.18272</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.36039</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.5241699999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.5326799999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.5425800000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.44003</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.22253</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.20674</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.18295</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.54344</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.48254</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.80857</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.58024</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.71815</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.80733</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52955</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80249</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.21829</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.21073</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.61839</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.60246</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.21944</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>1.18445</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.19504</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.20297</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.2093</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.20645</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.23082</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.22685</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.24631</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.20422</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.19465</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.19248</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.19298</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.23263</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.53398</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.47624</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.56383</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.21314</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.3934</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.20924</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.3684</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.61153</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.58297</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.19986</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.50443</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.44302</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.27196</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.62458</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71311</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45707</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.2013</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1.19236</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.24384</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.11841</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.20678</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.67095</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.31187</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.50908</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.01975</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.6288400000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60612</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.6125700000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.6009500000000001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.12034</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.14067</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.17911</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.60546</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.23982</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.5998300000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5977100000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46264</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.61373</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.61421</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.60142</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.59889</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18548</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.41649</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.29038</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.5928600000000001</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31876</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.53476</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.5687300000000001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19485</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.21657</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04468</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18224</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.01579</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.03666</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.18557</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20927</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06099</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.01114</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.7340099999999999</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46263</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48928</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34564</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.60327</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10264</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21739</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20727</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07153</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06977999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33232</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31494</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42784</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78527</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8686900000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5391900000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52632</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5650700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58741</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.71439</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87779</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46746</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55857</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8309500000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.58314</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8556900000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.64374</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6464800000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.3953</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34871</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18443</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19832</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44332</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.54843</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.69149</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78201</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6429199999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49384</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42209</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.47188</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48915</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.33596</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.71926</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.24622</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24898</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15644</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00787</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25412</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.68837</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.61164</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.80025</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41102</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44587</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31162</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.26524</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>1.3213</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.30596</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.31362</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.24908</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26918</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27674</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16007</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16528</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15681</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15605</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16009</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25207</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.15974</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25532</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.12989</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14512</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>1.38124</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>1.42833</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>1.41606</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1.41621</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33788</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42664</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26523</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23893</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.23724</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43091</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.20173</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27037</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35141</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48338</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.28806</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.85411</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.54504</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.47231</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.07283</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.52211</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.04399</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.31075</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.21433</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1.01102</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.16924</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.86607</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.6165499999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.69928</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.5640499999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.77887</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.72751</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.60302</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.9729500000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.02542</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.99558</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.62482</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.23973</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.48381</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.21413</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.22479</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.5854400000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.9301900000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.20429</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.8763500000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.13178</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.50511</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.2431</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.37185</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31934</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.7807500000000001</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.20788</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.18097</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34485</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.49235</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.72489</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.44089</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65208</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.16548</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.52635</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.48226</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33692</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.18149</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.09722</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.59093</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.5051600000000001</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.17555</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>-0.02426</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.62836</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21128</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.15504</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.14317</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.23781</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.09007</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.18115</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.11557</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.18923</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.69469</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.24644</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>1.40054</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.81696</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.66938</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35177</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.46376</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.54059</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.82475</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.63556</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.40123</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1.40148</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1.38941</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.51802</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46991</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50584</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.47096</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.2446</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.51813</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.55469</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.45024</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.63449</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.42948</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.36815</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.34993</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.35801</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.38481</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.71001</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.62424</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.60251</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.34879</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.34657</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.3466</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.34133</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.27408</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.33919</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.31336</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.3343</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.8318099999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48089</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48135</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.51598</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.64025</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.77847</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.86385</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.74275</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.13362</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.95862</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.08988</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.75554</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.7661</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66761</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.74052</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.90267</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.89576</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.03533</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15798</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21172</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43039</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34038</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.27565</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.27061</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.26647</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19551</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25903</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10497</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03636</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26631</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23895</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33022</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.25669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.25881</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.25879</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26289</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17547</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26795</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.22308</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14652</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01525</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04071</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03829</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01833</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03612</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20168</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26474</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33422</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.75494</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.64547</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.39052</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.45062</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25978</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.37462</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.71918</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8771100000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8479500000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.38279</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.16833</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.11111</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.20208</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00286</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00195</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.31581</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.49005</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25449</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1.21591</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.20096</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.34666</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.53666</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.80196</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.7774800000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7846799999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.36455</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97903</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.77847</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8430700000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.81086</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84109</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83927</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8435900000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.13969</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7727999999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.80679</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.77535</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.55269</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36678</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47371</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.62485</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.69729</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.58575</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49466</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.32554</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.49001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1.32849</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.32501</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1.32243</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1.31555</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.32017</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1.30138</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.35472</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.35028</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1.37412</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1.4705</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.48421</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.21046</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11202</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.16057</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>1.33374</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>1.31175</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>1.32356</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1.34106</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>1.32946</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>1.33154</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>1.32585</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.77073</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41337</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.62091</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47126</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1.49419</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>1.35925</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3452</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1.42873</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.15858</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.36351</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.58625</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.78871</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.56878</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.5101</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.57835</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.46431</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47476</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.21069</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7805</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.50826</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.2034</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.78654</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.73525</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.58278</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48686</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>1.43393</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>1.3867</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24044</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35807</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43044</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.49185</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.54434</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.73714</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.51755</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46368</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.48666</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.63851</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48506</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.70031</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74254</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.13297</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9345399999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.76288</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.79732</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36243</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.95877</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.95004</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.96121</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.95474</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.95414</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.96187</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.94428</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.9928899999999999</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.96163</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.9512699999999999</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.9580700000000001</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.88971</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.94721</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.94998</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.9568099999999999</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.95082</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.9520299999999999</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.96476</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.9689800000000001</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.96333</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.9943200000000001</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.9940099999999999</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.97163</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.96192</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.95931</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.9583400000000001</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.98798</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.9530700000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.96888</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.03816</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.10156</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.06359000000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.12876</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.13066</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.06228</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.13808</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.26632</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.07299</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11643</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.46555</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.4623</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.46443</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18281</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.33347</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.35874</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.35328</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.38319</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.32779</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.44987</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.41433</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.27839</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.16723</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17423</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.45723</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.45928</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36945</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9341799999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.58178</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.4837</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.39054</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1.5728</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.37275</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1.37511</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1.5891</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.57416</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1.57443</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1.59341</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1.35217</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.16741</v>
+      </c>
+      <c r="U142" t="n">
+        <v>1.36694</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.16675</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.21367</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.47827</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.32678</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.35275</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.20666</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.16093</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.16074</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1.17054</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.16846</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.19206</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.19242</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.17492</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.25423</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19436</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.1966</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42083</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.55523</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.5600700000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36191</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17531</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19755</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14041</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12199</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22711</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15454</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14365</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22563</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15329</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.19656</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19677</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.14339</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2800299999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.23026</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38673</v>
       </c>
     </row>
   </sheetData>
